--- a/stories/arbres/ATOM-LAN.NOM.001-01.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara et papa sont au jardin. Il y a un panier. Dedans, des pommes. Papa dit : on va compter des objets. Sara touche une pomme. Une. Elle en touche une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Sara dit : cinq pommes. Papa sourit. Il dit le nombre. Cinq. Sara pose les pommes. Une. Deux. Trois. Quatre. Cinq. Les objets sont là. Sara les compte. Le soleil chauffe le panier.</t>
+          <t>Sara et papa sont au jardin. Il y a un panier. Dedans, des pommes. On va compter des objets. Sara touche une pomme. Une. Elle en touche une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Cinq pommes. Papa sourit. Il dit le nombre. Cinq. Sara pose les pommes. Une. Deux. Trois. Quatre. Cinq. Les objets sont là. Sara les compte. Le soleil chauffe le panier.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sara et papa sont au jardin. Il y a un panier. Dedans, des pommes.
+papa|On va compter des objets.
+narrateur|Sara touche une pomme. Une. Elle en touche une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq.
+enfant-f|Cinq pommes. Papa sourit. Il dit le nombre. Cinq.
+narrateur|Sara pose les pommes. Une. Deux. Trois. Quatre. Cinq. Les objets sont là. Sara les compte. Le soleil chauffe le panier.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Sara compte les pommes. Combien y en a-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1659,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a compté des objets. Cinq pommes. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,6 +1822,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range le panier. Sara garde une pomme. Elle croque.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,6 +1989,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1967,7 +2012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1984,6 +2029,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-01.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Sara pose les pommes. Une. Deux. Trois. Quatre. Cinq. Les objets sont là. Sara les compte. Le soleil chauffe le panier.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Sara compte les pommes. Combien y en a-t-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1664,6 +1671,7 @@
           <t>narrateur|Sara a compté des objets. Cinq pommes. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1827,6 +1835,7 @@
           <t>narrateur|Papa range le panier. Sara garde une pomme. Elle croque.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1994,6 +2003,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2012,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2036,6 +2046,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2237,6 +2261,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.NOM.001-01.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sara compte les pommes</t>
+          <t>Sarah compte les pommes</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une abeille tourne près du panier. Sarah touche les pommes une à une. Elle dit le nombre. Papa et maman écoutent.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara et papa sont au jardin. Il y a un panier. Dedans, des pommes. On va compter des objets. Sara touche une pomme. Une. Elle en touche une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Cinq pommes. Papa sourit. Il dit le nombre. Cinq. Sara pose les pommes. Une. Deux. Trois. Quatre. Cinq. Les objets sont là. Sara les compte. Le soleil chauffe le panier.</t>
+          <t>Une abeille tourne près du panier. Ses ailes font un petit chant. Le bois du banc est tiède. Il sent le soleil. L'herbe colle un peu aux pieds. Elle est douce et verte. Un torchon bleu sèche sur la corde. Le torchon bouge tout doux. La maison est derrière les tomates. Ça sent les pommes mûres. Sarah, tu entends l'abeille ? Oui, papa. Elle chante. Elle est près du panier. Tout doux, l'abeille. En ce moment, le panier attend. Dedans, des pommes rouges. Le panier est en osier. L'osier gratte un peu. On compte des objets. On touche. On dit le nombre. Sarah touche une pomme. Une. Elle en touche une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Cinq pommes. Tu as dit le nombre. Cinq. Les pommes sont fraîches. La peau est lisse. Tu as compté des objets. Bravo, Sarah. C'est du bon travail. Papa pose encore des pommes. Sarah recommence. Une. Deux. Trois. Quatre. Cinq. Encore cinq. Tu dis le nombre ? Cinq. L'abeille s'éloigne. Le torchon claque un peu. On range le panier ? Oui, maman. Sarah pose une pomme. Le bois du banc reste tiède. Les objets sont là. On les a comptés. Une tomate brille près du banc. Elle est rouge et ronde. On compte aussi les tomates ? Oui, papa. Sarah touche une tomate. Une. Elle en touche une autre. Deux. Deux tomates. Tu dis le nombre. Deux. Bravo. Le torchon sèche encore. L'herbe reste douce.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,79 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sara et papa sont au jardin. Il y a un panier. Dedans, des pommes.
-papa|On va compter des objets.
-narrateur|Sara touche une pomme. Une. Elle en touche une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq.
-enfant-f|Cinq pommes. Papa sourit. Il dit le nombre. Cinq.
-narrateur|Sara pose les pommes. Une. Deux. Trois. Quatre. Cinq. Les objets sont là. Sara les compte. Le soleil chauffe le panier.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une abeille tourne près du panier.
+narrateur|Ses ailes font un petit chant.
+narrateur|Le bois du banc est tiède.
+narrateur|Il sent le soleil.
+narrateur|L'herbe colle un peu aux pieds.
+narrateur|Elle est douce et verte.
+narrateur|Un torchon bleu sèche sur la corde.
+narrateur|Le torchon bouge tout doux.
+narrateur|La maison est derrière les tomates.
+narrateur|Ça sent les pommes mûres.
+papa|Sarah, tu entends l'abeille ?
+enfant-f|Oui, papa.
+enfant-f|Elle chante.
+maman|Elle est près du panier.
+papa|Tout doux, l'abeille.
+narrateur|En ce moment, le panier attend.
+narrateur|Dedans, des pommes rouges.
+narrateur|Le panier est en osier.
+narrateur|L'osier gratte un peu.
+maman|On compte des objets.
+papa|On touche. On dit le nombre.
+narrateur|Sarah touche une pomme.
+enfant-f|Une.
+narrateur|Elle en touche une autre.
+enfant-f|Deux.
+narrateur|Encore une.
+enfant-f|Trois.
+narrateur|Encore une.
+enfant-f|Quatre.
+narrateur|Encore une.
+enfant-f|Cinq.
+papa|Cinq pommes.
+maman|Tu as dit le nombre.
+enfant-f|Cinq.
+narrateur|Les pommes sont fraîches.
+narrateur|La peau est lisse.
+papa|Tu as compté des objets.
+papa|Bravo, Sarah.
+maman|C'est du bon travail.
+narrateur|Papa pose encore des pommes.
+narrateur|Sarah recommence.
+enfant-f|Une.
+enfant-f|Deux.
+enfant-f|Trois.
+enfant-f|Quatre.
+enfant-f|Cinq.
+maman|Encore cinq.
+papa|Tu dis le nombre ?
+enfant-f|Cinq.
+narrateur|L'abeille s'éloigne.
+narrateur|Le torchon claque un peu.
+maman|On range le panier ?
+enfant-f|Oui, maman.
+narrateur|Sarah pose une pomme.
+narrateur|Le bois du banc reste tiède.
+papa|Les objets sont là.
+maman|On les a comptés.
+narrateur|Une tomate brille près du banc.
+narrateur|Elle est rouge et ronde.
+papa|On compte aussi les tomates ?
+enfant-f|Oui, papa.
+narrateur|Sarah touche une tomate.
+enfant-f|Une.
+narrateur|Elle en touche une autre.
+enfant-f|Deux.
+maman|Deux tomates.
+papa|Tu dis le nombre.
+enfant-f|Deux.
+maman|Bravo.
+narrateur|Le torchon sèche encore.
+narrateur|L'herbe reste douce.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1421,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Sara compte les pommes. Combien y en a-t-il ?</t>
+          <t>Sarah compte les pommes. Combien y en a-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,10 +1577,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Sara compte les pommes. Combien y en a-t-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Sarah compte les pommes.
+narrateur|Combien y en a-t-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,7 +1605,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara a compté des objets. Cinq pommes. Elle a dit le nombre.</t>
+          <t>Sarah a compté des objets. Cinq pommes. Elle a dit le nombre. Tu as dit cinq ? Oui, papa. Bravo, Sarah. Tu as fait du bon travail. Le panier repose sur le banc. L'osier est un peu rêche. Les pommes sont à leur place ? Oui, papa. Une pomme brille encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1668,10 +1745,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sara a compté des objets. Cinq pommes. Elle a dit le nombre.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah a compté des objets.
+narrateur|Cinq pommes.
+narrateur|Elle a dit le nombre.
+papa|Tu as dit cinq ?
+enfant-f|Oui, papa.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+narrateur|Le panier repose sur le banc.
+narrateur|L'osier est un peu rêche.
+papa|Les pommes sont à leur place ?
+enfant-f|Oui, papa.
+narrateur|Une pomme brille encore.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1696,7 +1783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le panier. Sara garde une pomme. Elle croque.</t>
+          <t>Sarah pose le torchon. Je te tiens le panier ? Oui, maman. Maman tient l'anse. L'anse est un peu ronde. Tu as fini de compter ? Oui, papa. Bravo. Le banc reste tiède. On rentre les pommes ? Oui. Ça sent encore le soleil.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1832,10 +1919,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range le panier. Sara garde une pomme. Elle croque.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Sarah pose le torchon.
+maman|Je te tiens le panier ?
+enfant-f|Oui, maman.
+narrateur|Maman tient l'anse.
+narrateur|L'anse est un peu ronde.
+papa|Tu as fini de compter ?
+enfant-f|Oui, papa.
+papa|Bravo.
+narrateur|Le banc reste tiède.
+maman|On rentre les pommes ?
+enfant-f|Oui.
+narrateur|Ça sent encore le soleil.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1860,7 +1957,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah tient une pomme. La peau est lisse. Merci d'avoir compté. On touche. On dit le nombre. Oui. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2000,10 +2097,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Sarah tient une pomme.
+narrateur|La peau est lisse.
+maman|Merci d'avoir compté.
+papa|On touche. On dit le nombre.
+enfant-f|Oui.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2060,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-01.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-01.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sarah compte les pommes</t>
+          <t>Les pommes tièdes de Mila</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Une abeille tourne près du panier. Sarah touche les pommes une à une. Elle dit le nombre. Papa et maman écoutent.</t>
+          <t>Une abeille tourne. Mila touche les pommes une à une. Une. Deux. Trois. Quatre. Cinq. Elle dit le nombre.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une abeille tourne près du panier. Ses ailes font un petit chant. Le bois du banc est tiède. Il sent le soleil. L'herbe colle un peu aux pieds. Elle est douce et verte. Un torchon bleu sèche sur la corde. Le torchon bouge tout doux. La maison est derrière les tomates. Ça sent les pommes mûres. Sarah, tu entends l'abeille ? Oui, papa. Elle chante. Elle est près du panier. Tout doux, l'abeille. En ce moment, le panier attend. Dedans, des pommes rouges. Le panier est en osier. L'osier gratte un peu. On compte des objets. On touche. On dit le nombre. Sarah touche une pomme. Une. Elle en touche une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Cinq pommes. Tu as dit le nombre. Cinq. Les pommes sont fraîches. La peau est lisse. Tu as compté des objets. Bravo, Sarah. C'est du bon travail. Papa pose encore des pommes. Sarah recommence. Une. Deux. Trois. Quatre. Cinq. Encore cinq. Tu dis le nombre ? Cinq. L'abeille s'éloigne. Le torchon claque un peu. On range le panier ? Oui, maman. Sarah pose une pomme. Le bois du banc reste tiède. Les objets sont là. On les a comptés. Une tomate brille près du banc. Elle est rouge et ronde. On compte aussi les tomates ? Oui, papa. Sarah touche une tomate. Une. Elle en touche une autre. Deux. Deux tomates. Tu dis le nombre. Deux. Bravo. Le torchon sèche encore. L'herbe reste douce.</t>
+          <t>Une abeille tourne autour d'une fleur. L'herbe est chaude sous les pieds. Le pommier fait une ombre ronde. Un panier d'osier attend. Il sent le bois sec. Une pierre tiède est près du tronc. Une feuille tombe, tout doux. Un oiseau fait un petit cri. Le vent sent l'herbe coupée. Tu as vu l'abeille, Mila ? Oui, papa. Elle tourne. Elle aime la fleur. En ce moment, Mila s'assoit. Le panier est près d'elle. Dedans, des pommes. Elles sentent le sucre. On va compter des objets. Des pommes. Des pommes. Mila touche une pomme. Elle est lisse et tiède. Une. Une. Elle en touche une autre. Deux. Deux. Encore une. Trois. Trois. Encore une. Quatre. Quatre. Encore une. Cinq. Cinq. Cinq pommes. Tu as dit le nombre. Cinq. Bravo, Mila. Tu as compté des objets. C'est du bon travail. Le soleil chauffe le panier. On pose les pommes ? Oui, papa. Mila pose une pomme. Une. Elle en pose une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Les objets sont là. Tu les as comptés. Cinq. Oui. Tu as dit le nombre. L'abeille s'éloigne un peu. L'herbe chatouille le genou de Mila. Ça sent bon, hein ? Ça sent la pomme. Oui. Un oiseau picore une miette d'herbe. La pierre tiède reste près du tronc. Tu as fini de compter ? Oui, papa. Cinq. Bravo. Tu as compté des objets. Une feuille tourne, tout lentement. L'ombre du pommier bouge un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sara et papa sont au jardin. Il y a un panier. Dedans, des pommes. Papa dit : on va &lt;emphasis level="moderate"&gt;compter&lt;/emphasis&gt; des objets. Sara touche une pomme. Une. Elle en touche une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Sara dit : cinq pommes. Papa sourit. Il dit le nombre. Cinq. Sara pose les pommes. Une. Deux. Trois. Quatre. Cinq. Les objets sont là. Sara les compte. Le soleil chauffe le panier.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une abeille tourne autour d'une fleur. L'herbe est chaude sous les pieds. Le pommier fait une ombre ronde. Un panier d'osier attend. Il sent le bois sec. Une pierre tiède est près du tronc. Une feuille tombe, tout doux. Un oiseau fait un petit cri. Le vent sent l'herbe coupée. Tu as vu l'abeille, Mila ? Oui, papa. Elle tourne. Elle aime la fleur. En ce moment, Mila s'assoit. Le panier est près d'elle. Dedans, des pommes. Elles sentent le sucre. On va compter des objets. Des pommes. Des pommes. Mila touche une pomme. Elle est lisse et tiède. Une. Une. Elle en touche une autre. Deux. Deux. Encore une. Trois. Trois. Encore une. Quatre. Quatre. Encore une. Cinq. Cinq. Cinq pommes. Tu as dit le nombre. Cinq. Bravo, Mila. Tu as compté des objets. C'est du bon travail. Le soleil chauffe le panier. On pose les pommes ? Oui, papa. Mila pose une pomme. Une. Elle en pose une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Les objets sont là. Tu les as comptés. Cinq. Oui. Tu as dit le nombre. L'abeille s'éloigne un peu. L'herbe chatouille le genou de Mila. Ça sent bon, hein ? Ça sent la pomme. Oui. Un oiseau picore une miette d'herbe. La pierre tiède reste près du tronc. Tu as fini de compter ? Oui, papa. Cinq. Bravo. Tu as compté des objets. Une feuille tourne, tout lentement. L'ombre du pommier bouge un peu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1324,30 +1324,54 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Une abeille tourne près du panier.
-narrateur|Ses ailes font un petit chant.
-narrateur|Le bois du banc est tiède.
-narrateur|Il sent le soleil.
-narrateur|L'herbe colle un peu aux pieds.
-narrateur|Elle est douce et verte.
-narrateur|Un torchon bleu sèche sur la corde.
-narrateur|Le torchon bouge tout doux.
-narrateur|La maison est derrière les tomates.
-narrateur|Ça sent les pommes mûres.
-papa|Sarah, tu entends l'abeille ?
+          <t>narrateur|Une abeille tourne autour d'une fleur.
+narrateur|L'herbe est chaude sous les pieds.
+narrateur|Le pommier fait une ombre ronde.
+narrateur|Un panier d'osier attend.
+narrateur|Il sent le bois sec.
+narrateur|Une pierre tiède est près du tronc.
+narrateur|Une feuille tombe, tout doux.
+narrateur|Un oiseau fait un petit cri.
+narrateur|Le vent sent l'herbe coupée.
+papa|Tu as vu l'abeille, Mila ?
 enfant-f|Oui, papa.
-enfant-f|Elle chante.
-maman|Elle est près du panier.
-papa|Tout doux, l'abeille.
-narrateur|En ce moment, le panier attend.
-narrateur|Dedans, des pommes rouges.
-narrateur|Le panier est en osier.
-narrateur|L'osier gratte un peu.
-maman|On compte des objets.
-papa|On touche. On dit le nombre.
-narrateur|Sarah touche une pomme.
+enfant-f|Elle tourne.
+papa|Elle aime la fleur.
+narrateur|En ce moment, Mila s'assoit.
+narrateur|Le panier est près d'elle.
+narrateur|Dedans, des pommes.
+narrateur|Elles sentent le sucre.
+papa|On va compter des objets.
+papa|Des pommes.
+enfant-f|Des pommes.
+narrateur|Mila touche une pomme.
+narrateur|Elle est lisse et tiède.
+papa|Une.
 enfant-f|Une.
 narrateur|Elle en touche une autre.
+papa|Deux.
+enfant-f|Deux.
+narrateur|Encore une.
+papa|Trois.
+enfant-f|Trois.
+narrateur|Encore une.
+papa|Quatre.
+enfant-f|Quatre.
+narrateur|Encore une.
+papa|Cinq.
+enfant-f|Cinq.
+enfant-f|Cinq pommes.
+papa|Tu as dit le nombre.
+papa|Cinq.
+papa|Bravo, Mila.
+papa|Tu as compté des objets.
+papa|C'est du bon travail.
+narrateur|Le soleil chauffe le panier.
+papa|On pose les pommes ?
+enfant-f|Oui, papa.
+narrateur|Mila pose une pomme.
+enfant-f|Une.
+narrateur|Elle en pose une autre.
 enfant-f|Deux.
 narrateur|Encore une.
 enfant-f|Trois.
@@ -1355,46 +1379,25 @@
 enfant-f|Quatre.
 narrateur|Encore une.
 enfant-f|Cinq.
-papa|Cinq pommes.
-maman|Tu as dit le nombre.
+papa|Les objets sont là.
+papa|Tu les as comptés.
 enfant-f|Cinq.
-narrateur|Les pommes sont fraîches.
-narrateur|La peau est lisse.
+papa|Oui.
+papa|Tu as dit le nombre.
+narrateur|L'abeille s'éloigne un peu.
+narrateur|L'herbe chatouille le genou de Mila.
+papa|Ça sent bon, hein ?
+enfant-f|Ça sent la pomme.
+papa|Oui.
+narrateur|Un oiseau picore une miette d'herbe.
+narrateur|La pierre tiède reste près du tronc.
+papa|Tu as fini de compter ?
+enfant-f|Oui, papa.
+enfant-f|Cinq.
+papa|Bravo.
 papa|Tu as compté des objets.
-papa|Bravo, Sarah.
-maman|C'est du bon travail.
-narrateur|Papa pose encore des pommes.
-narrateur|Sarah recommence.
-enfant-f|Une.
-enfant-f|Deux.
-enfant-f|Trois.
-enfant-f|Quatre.
-enfant-f|Cinq.
-maman|Encore cinq.
-papa|Tu dis le nombre ?
-enfant-f|Cinq.
-narrateur|L'abeille s'éloigne.
-narrateur|Le torchon claque un peu.
-maman|On range le panier ?
-enfant-f|Oui, maman.
-narrateur|Sarah pose une pomme.
-narrateur|Le bois du banc reste tiède.
-papa|Les objets sont là.
-maman|On les a comptés.
-narrateur|Une tomate brille près du banc.
-narrateur|Elle est rouge et ronde.
-papa|On compte aussi les tomates ?
-enfant-f|Oui, papa.
-narrateur|Sarah touche une tomate.
-enfant-f|Une.
-narrateur|Elle en touche une autre.
-enfant-f|Deux.
-maman|Deux tomates.
-papa|Tu dis le nombre.
-enfant-f|Deux.
-maman|Bravo.
-narrateur|Le torchon sèche encore.
-narrateur|L'herbe reste douce.</t>
+narrateur|Une feuille tourne, tout lentement.
+narrateur|L'ombre du pommier bouge un peu.</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1424,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Sarah compte les pommes. Combien y en a-t-il ?</t>
+          <t>Mila compte les pommes. Combien y en a-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sara compte les pommes. Combien y en a-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila compte les pommes. Combien y en a-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1577,7 +1580,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Sarah compte les pommes.
+          <t>narrateur|Mila compte les pommes.
 narrateur|Combien y en a-t-il ?</t>
         </is>
       </c>
@@ -1605,12 +1608,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a compté des objets. Cinq pommes. Elle a dit le nombre. Tu as dit cinq ? Oui, papa. Bravo, Sarah. Tu as fait du bon travail. Le panier repose sur le banc. L'osier est un peu rêche. Les pommes sont à leur place ? Oui, papa. Une pomme brille encore.</t>
+          <t>Mila a compté des objets. Cinq pommes. Elle a dit le nombre. Cinq. Bravo, Mila. Cinq pommes. Tu as fait du bon travail. Le panier est un peu lourd. Le soleil tient encore l'ombre ronde.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sara a compté des objets. Cinq pommes. Elle a dit le nombre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a compté des objets. Cinq pommes. Elle a dit le nombre. Cinq. Bravo, Mila. Cinq pommes. Tu as fait du bon travail. Le panier est un peu lourd. Le soleil tient encore l'ombre ronde.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1745,18 +1748,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sarah a compté des objets.
+          <t>narrateur|Mila a compté des objets.
 narrateur|Cinq pommes.
 narrateur|Elle a dit le nombre.
-papa|Tu as dit cinq ?
-enfant-f|Oui, papa.
-maman|Bravo, Sarah.
-maman|Tu as fait du bon travail.
-narrateur|Le panier repose sur le banc.
-narrateur|L'osier est un peu rêche.
-papa|Les pommes sont à leur place ?
-enfant-f|Oui, papa.
-narrateur|Une pomme brille encore.</t>
+papa|Cinq.
+papa|Bravo, Mila.
+enfant-f|Cinq pommes.
+papa|Tu as fait du bon travail.
+narrateur|Le panier est un peu lourd.
+narrateur|Le soleil tient encore l'ombre ronde.</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sarah pose le torchon. Je te tiens le panier ? Oui, maman. Maman tient l'anse. L'anse est un peu ronde. Tu as fini de compter ? Oui, papa. Bravo. Le banc reste tiède. On rentre les pommes ? Oui. Ça sent encore le soleil.</t>
+          <t>On range le panier ? Oui, papa. Papa range le panier. Mila garde une pomme. Tu croques ? Oui. Elle croque. Ça croque tout fort. Tu as fini ta bouchée ? Oui, papa. Bravo. La pierre tiède reste près du tronc. L'abeille est loin, maintenant. On rentre avec le panier ? Oui, papa. Le panier sent encore les pommes.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa range le panier. Sara garde une pomme. Elle croque.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On range le panier ? Oui, papa. Papa range le panier. Mila garde une pomme. Tu croques ? Oui. Elle croque. Ça croque tout fort. Tu as fini ta bouchée ? Oui, papa. Bravo. La pierre tiède reste près du tronc. L'abeille est loin, maintenant. On rentre avec le panier ? Oui, papa. Le panier sent encore les pommes.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1919,18 +1919,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sarah pose le torchon.
-maman|Je te tiens le panier ?
-enfant-f|Oui, maman.
-narrateur|Maman tient l'anse.
-narrateur|L'anse est un peu ronde.
-papa|Tu as fini de compter ?
+          <t>papa|On range le panier ?
+enfant-f|Oui, papa.
+narrateur|Papa range le panier.
+narrateur|Mila garde une pomme.
+papa|Tu croques ?
+enfant-f|Oui.
+narrateur|Elle croque.
+narrateur|Ça croque tout fort.
+papa|Tu as fini ta bouchée ?
 enfant-f|Oui, papa.
 papa|Bravo.
-narrateur|Le banc reste tiède.
-maman|On rentre les pommes ?
-enfant-f|Oui.
-narrateur|Ça sent encore le soleil.</t>
+narrateur|La pierre tiède reste près du tronc.
+narrateur|L'abeille est loin, maintenant.
+papa|On rentre avec le panier ?
+enfant-f|Oui, papa.
+narrateur|Le panier sent encore les pommes.</t>
         </is>
       </c>
     </row>
@@ -1957,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Sarah tient une pomme. La peau est lisse. Merci d'avoir compté. On touche. On dit le nombre. Oui. L'histoire est finie.</t>
+          <t>Cinq pommes. Tu as compté des objets. Tu as dit le nombre. Bravo, Mila. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Cinq pommes. Tu as compté des objets. Tu as dit le nombre. Bravo, Mila. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2097,11 +2101,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Sarah tient une pomme.
-narrateur|La peau est lisse.
-maman|Merci d'avoir compté.
-papa|On touche. On dit le nombre.
-enfant-f|Oui.
+          <t>enfant-f|Cinq pommes.
+papa|Tu as compté des objets.
+papa|Tu as dit le nombre.
+papa|Bravo, Mila.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2123,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2171,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-01.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une abeille tourne autour d'une fleur. L'herbe est chaude sous les pieds. Le pommier fait une ombre ronde. Un panier d'osier attend. Il sent le bois sec. Une pierre tiède est près du tronc. Une feuille tombe, tout doux. Un oiseau fait un petit cri. Le vent sent l'herbe coupée. Tu as vu l'abeille, Mila ? Oui, papa. Elle tourne. Elle aime la fleur. En ce moment, Mila s'assoit. Le panier est près d'elle. Dedans, des pommes. Elles sentent le sucre. On va compter des objets. Des pommes. Des pommes. Mila touche une pomme. Elle est lisse et tiède. Une. Une. Elle en touche une autre. Deux. Deux. Encore une. Trois. Trois. Encore une. Quatre. Quatre. Encore une. Cinq. Cinq. Cinq pommes. Tu as dit le nombre. Cinq. Bravo, Mila. Tu as compté des objets. C'est du bon travail. Le soleil chauffe le panier. On pose les pommes ? Oui, papa. Mila pose une pomme. Une. Elle en pose une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Les objets sont là. Tu les as comptés. Cinq. Oui. Tu as dit le nombre. L'abeille s'éloigne un peu. L'herbe chatouille le genou de Mila. Ça sent bon, hein ? Ça sent la pomme. Oui. Un oiseau picore une miette d'herbe. La pierre tiède reste près du tronc. Tu as fini de compter ? Oui, papa. Cinq. Bravo. Tu as compté des objets. Une feuille tourne, tout lentement. L'ombre du pommier bouge un peu.</t>
+          <t>Une abeille tourne autour d'une fleur. L'herbe est chaude sous les pieds. Le pommier fait une ombre ronde. Un panier d'osier attend. Il sent le bois sec. Une pierre tiède est près du tronc. Une feuille tombe, tout doux. Un oiseau fait un petit cri. Le vent sent l'herbe coupée. Tu as vu l'abeille, Mila ? Oui, papa. Elle tourne. Elle aime la fleur. En ce moment, Mila s'assoit. Le panier est près d'elle. Dedans, des pommes. Elles sentent le sucre. On va compter des objets. Des pommes. Des pommes. Mila touche une pomme. Elle est lisse et tiède. Une. Une. Elle en touche une autre. Deux. Deux. Encore une. Trois. Trois. Encore une. Quatre. Quatre. Encore une. Cinq. Cinq. Cinq pommes. Tu as dit le nombre. Cinq. Bravo, Mila. Tu as compté des objets. Le soleil chauffe le panier. On pose les pommes ? Oui, papa. Mila pose une pomme. Une. Elle en pose une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Les objets sont là. Tu les as comptés. Cinq. Oui. Tu as dit le nombre. L'abeille s'éloigne un peu. L'herbe chatouille le genou de Mila. Ça sent bon, hein ? Ça sent la pomme. Oui. Un oiseau picore une miette d'herbe. La pierre tiède reste près du tronc. Tu as fini de compter ? Oui, papa. Cinq. Bravo. Tu as compté des objets. Une feuille tourne, tout lentement. L'ombre du pommier bouge un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Une abeille tourne autour d'une fleur. L'herbe est chaude sous les pieds. Le pommier fait une ombre ronde. Un panier d'osier attend. Il sent le bois sec. Une pierre tiède est près du tronc. Une feuille tombe, tout doux. Un oiseau fait un petit cri. Le vent sent l'herbe coupée. Tu as vu l'abeille, Mila ? Oui, papa. Elle tourne. Elle aime la fleur. En ce moment, Mila s'assoit. Le panier est près d'elle. Dedans, des pommes. Elles sentent le sucre. On va compter des objets. Des pommes. Des pommes. Mila touche une pomme. Elle est lisse et tiède. Une. Une. Elle en touche une autre. Deux. Deux. Encore une. Trois. Trois. Encore une. Quatre. Quatre. Encore une. Cinq. Cinq. Cinq pommes. Tu as dit le nombre. Cinq. Bravo, Mila. Tu as compté des objets. C'est du bon travail. Le soleil chauffe le panier. On pose les pommes ? Oui, papa. Mila pose une pomme. Une. Elle en pose une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Les objets sont là. Tu les as comptés. Cinq. Oui. Tu as dit le nombre. L'abeille s'éloigne un peu. L'herbe chatouille le genou de Mila. Ça sent bon, hein ? Ça sent la pomme. Oui. Un oiseau picore une miette d'herbe. La pierre tiède reste près du tronc. Tu as fini de compter ? Oui, papa. Cinq. Bravo. Tu as compté des objets. Une feuille tourne, tout lentement. L'ombre du pommier bouge un peu.</t>
+          <t>Une abeille tourne autour d'une fleur. L'herbe est chaude sous les pieds. Le pommier fait une ombre ronde. Un panier d'osier attend. Il sent le bois sec. Une pierre tiède est près du tronc. Une feuille tombe, tout doux. Un oiseau fait un petit cri. Le vent sent l'herbe coupée. Tu as vu l'abeille, Mila ? Oui, papa. Elle tourne. Elle aime la fleur. En ce moment, Mila s'assoit. Le panier est près d'elle. Dedans, des pommes. Elles sentent le sucre. On va compter des objets. Des pommes. Des pommes. Mila touche une pomme. Elle est lisse et tiède. Une. Une. Elle en touche une autre. Deux. Deux. Encore une. Trois. Trois. Encore une. Quatre. Quatre. Encore une. Cinq. Cinq. Cinq pommes. Tu as dit le nombre. Cinq. Bravo, Mila. Tu as compté des objets. Le soleil chauffe le panier. On pose les pommes ? Oui, papa. Mila pose une pomme. Une. Elle en pose une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Les objets sont là. Tu les as comptés. Cinq. Oui. Tu as dit le nombre. L'abeille s'éloigne un peu. L'herbe chatouille le genou de Mila. Ça sent bon, hein ? Ça sent la pomme. Oui. Un oiseau picore une miette d'herbe. La pierre tiède reste près du tronc. Tu as fini de compter ? Oui, papa. Cinq. Bravo. Tu as compté des objets. Une feuille tourne, tout lentement. L'ombre du pommier bouge un peu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1365,7 +1365,6 @@
 papa|Cinq.
 papa|Bravo, Mila.
 papa|Tu as compté des objets.
-papa|C'est du bon travail.
 narrateur|Le soleil chauffe le panier.
 papa|On pose les pommes ?
 enfant-f|Oui, papa.
@@ -1608,12 +1607,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a compté des objets. Cinq pommes. Elle a dit le nombre. Cinq. Bravo, Mila. Cinq pommes. Tu as fait du bon travail. Le panier est un peu lourd. Le soleil tient encore l'ombre ronde.</t>
+          <t>Mila a compté des objets. Cinq pommes. Elle a dit le nombre. Cinq. Bravo, Mila. Cinq pommes. Le panier est un peu lourd. Le soleil tient encore l'ombre ronde.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Mila a compté des objets. Cinq pommes. Elle a dit le nombre. Cinq. Bravo, Mila. Cinq pommes. Tu as fait du bon travail. Le panier est un peu lourd. Le soleil tient encore l'ombre ronde.</t>
+          <t>Mila a compté des objets. Cinq pommes. Elle a dit le nombre. Cinq. Bravo, Mila. Cinq pommes. Le panier est un peu lourd. Le soleil tient encore l'ombre ronde.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1754,7 +1753,6 @@
 papa|Cinq.
 papa|Bravo, Mila.
 enfant-f|Cinq pommes.
-papa|Tu as fait du bon travail.
 narrateur|Le panier est un peu lourd.
 narrateur|Le soleil tient encore l'ombre ronde.</t>
         </is>
@@ -1961,12 +1959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Cinq pommes. Tu as compté des objets. Tu as dit le nombre. Bravo, Mila. L'histoire est finie.</t>
+          <t>Cinq pommes. Tu as compté des objets. Tu as dit le nombre. Bravo, Mila.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Cinq pommes. Tu as compté des objets. Tu as dit le nombre. Bravo, Mila. L'histoire est finie.</t>
+          <t>Cinq pommes. Tu as compté des objets. Tu as dit le nombre. Bravo, Mila.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2104,8 +2102,7 @@
           <t>enfant-f|Cinq pommes.
 papa|Tu as compté des objets.
 papa|Tu as dit le nombre.
-papa|Bravo, Mila.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Mila.</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2176,6 +2173,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-LAN.NOM.001-01.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>jardin, sous le pommier</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sara, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
